--- a/output/Tables/Scenarios/HIA_add_scenarios.xlsx
+++ b/output/Tables/Scenarios/HIA_add_scenarios.xlsx
@@ -1,21 +1,77 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Scenarios/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264DAE72-0F76-3A4C-B30E-748E2709A93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>Best case scenario</t>
+  </si>
+  <si>
+    <t>Modal shift scenario</t>
+  </si>
+  <si>
+    <t>Best practice scenario</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +119,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +171,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +205,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +240,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,81 +416,71 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>749171.939</v>
+        <v>749171.93900000001</v>
       </c>
       <c r="B2">
-        <v>739181.1360000001</v>
+        <v>739181.13600000006</v>
       </c>
       <c r="C2">
-        <v>759107.7250000001</v>
+        <v>759107.72500000009</v>
       </c>
       <c r="D2">
         <v>1513284.632</v>
@@ -436,7 +492,7 @@
         <v>1529218.179</v>
       </c>
       <c r="G2">
-        <v>9585513523.317001</v>
+        <v>9585513523.3170013</v>
       </c>
       <c r="H2">
         <v>9431146725.460001</v>
@@ -445,95 +501,89 @@
         <v>203379184933.759</v>
       </c>
       <c r="J2">
-        <v>201268309936.555</v>
+        <v>201268309936.55499</v>
       </c>
       <c r="K2">
         <v>199147675007.879</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Best case scenario</t>
-        </is>
+      <c r="L2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>68790.304</v>
+        <v>68790.304000000004</v>
       </c>
       <c r="B3">
-        <v>66630.64900000003</v>
+        <v>66630.649000000034</v>
       </c>
       <c r="C3">
-        <v>71050.75599999999</v>
+        <v>71050.755999999994</v>
       </c>
       <c r="D3">
-        <v>158011.2120000001</v>
+        <v>158011.21200000009</v>
       </c>
       <c r="E3">
-        <v>154397.213</v>
+        <v>154397.21299999999</v>
       </c>
       <c r="F3">
-        <v>161797.5749999998</v>
+        <v>161797.57499999981</v>
       </c>
       <c r="G3">
-        <v>865035502.4180012</v>
+        <v>865035502.41800117</v>
       </c>
       <c r="H3">
-        <v>836710268.915</v>
+        <v>836710268.91499996</v>
       </c>
       <c r="I3">
         <v>21522856907.521</v>
       </c>
       <c r="J3">
-        <v>21014333824.20601</v>
+        <v>21014333824.206009</v>
       </c>
       <c r="K3">
-        <v>20542800374.77501</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Modal shift scenario</t>
-        </is>
+        <v>20542800374.775009</v>
+      </c>
+      <c r="L3" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>59192.67999999999</v>
+        <v>59192.679999999993</v>
       </c>
       <c r="B4">
-        <v>63567.05599999998</v>
+        <v>63567.055999999982</v>
       </c>
       <c r="C4">
-        <v>54581.28699999989</v>
+        <v>54581.286999999887</v>
       </c>
       <c r="D4">
-        <v>378940.9230000001</v>
+        <v>378940.92300000013</v>
       </c>
       <c r="E4">
-        <v>381107.5409999999</v>
+        <v>381107.54099999991</v>
       </c>
       <c r="F4">
-        <v>376174.313</v>
+        <v>376174.31300000002</v>
       </c>
       <c r="G4">
-        <v>880147950.7789998</v>
+        <v>880147950.77899981</v>
       </c>
       <c r="H4">
-        <v>935467385.118</v>
+        <v>935467385.11800003</v>
       </c>
       <c r="I4">
-        <v>50033309856.3251</v>
+        <v>50033309856.325104</v>
       </c>
       <c r="J4">
-        <v>50400560778.573</v>
+        <v>50400560778.572998</v>
       </c>
       <c r="K4">
-        <v>50685755987.37599</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Best practice scenario</t>
-        </is>
+        <v>50685755987.375992</v>
+      </c>
+      <c r="L4" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Scenarios/HIA_add_scenarios.xlsx
+++ b/output/Tables/Scenarios/HIA_add_scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Scenarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264DAE72-0F76-3A4C-B30E-748E2709A93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC44103C-DDF8-1341-B4EE-8BF190A2A9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="23060" windowHeight="10520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>tot_cases</t>
   </si>
@@ -46,13 +46,16 @@
     <t>tot_medic_costs_low</t>
   </si>
   <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
     <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
   </si>
   <si>
     <t>scenario</t>
@@ -417,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -428,13 +431,14 @@
     <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,8 +475,11 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>749171.93900000001</v>
       </c>
@@ -498,7 +505,7 @@
         <v>9431146725.460001</v>
       </c>
       <c r="I2">
-        <v>203379184933.759</v>
+        <v>9741544352.5569992</v>
       </c>
       <c r="J2">
         <v>201268309936.55499</v>
@@ -506,11 +513,14 @@
       <c r="K2">
         <v>199147675007.879</v>
       </c>
-      <c r="L2" t="s">
-        <v>12</v>
+      <c r="L2">
+        <v>203379184933.759</v>
+      </c>
+      <c r="M2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>68790.304000000004</v>
       </c>
@@ -535,20 +545,20 @@
       <c r="H3">
         <v>836710268.91499996</v>
       </c>
-      <c r="I3">
-        <v>21522856907.521</v>
-      </c>
       <c r="J3">
         <v>21014333824.206009</v>
       </c>
       <c r="K3">
         <v>20542800374.775009</v>
       </c>
-      <c r="L3" t="s">
-        <v>13</v>
+      <c r="L3">
+        <v>21522856907.521</v>
+      </c>
+      <c r="M3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>59192.679999999993</v>
       </c>
@@ -574,7 +584,7 @@
         <v>935467385.11800003</v>
       </c>
       <c r="I4">
-        <v>50033309856.325104</v>
+        <v>821816747.11900043</v>
       </c>
       <c r="J4">
         <v>50400560778.572998</v>
@@ -582,8 +592,11 @@
       <c r="K4">
         <v>50685755987.375992</v>
       </c>
-      <c r="L4" t="s">
-        <v>14</v>
+      <c r="L4">
+        <v>50033309856.325104</v>
+      </c>
+      <c r="M4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Scenarios/HIA_add_scenarios.xlsx
+++ b/output/Tables/Scenarios/HIA_add_scenarios.xlsx
@@ -1,80 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Scenarios/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC44103C-DDF8-1341-B4EE-8BF190A2A9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="23060" windowHeight="10520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>scenario</t>
-  </si>
-  <si>
-    <t>Best case scenario</t>
-  </si>
-  <si>
-    <t>Modal shift scenario</t>
-  </si>
-  <si>
-    <t>Best practice scenario</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -174,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -208,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -243,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -419,75 +350,86 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2">
-        <v>749171.93900000001</v>
+        <v>749171.939</v>
       </c>
       <c r="B2">
-        <v>739181.13600000006</v>
+        <v>739181.1360000001</v>
       </c>
       <c r="C2">
-        <v>759107.72500000009</v>
+        <v>759107.7250000001</v>
       </c>
       <c r="D2">
         <v>1513284.632</v>
@@ -499,16 +441,16 @@
         <v>1529218.179</v>
       </c>
       <c r="G2">
-        <v>9585513523.3170013</v>
+        <v>9585513523.317001</v>
       </c>
       <c r="H2">
         <v>9431146725.460001</v>
       </c>
       <c r="I2">
-        <v>9741544352.5569992</v>
+        <v>9741544352.556999</v>
       </c>
       <c r="J2">
-        <v>201268309936.55499</v>
+        <v>201268309936.555</v>
       </c>
       <c r="K2">
         <v>199147675007.879</v>
@@ -516,87 +458,96 @@
       <c r="L2">
         <v>203379184933.759</v>
       </c>
-      <c r="M2" t="s">
-        <v>13</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Best case scenario</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3">
-        <v>68790.304000000004</v>
+        <v>68790.304</v>
       </c>
       <c r="B3">
-        <v>66630.649000000034</v>
+        <v>66630.64900000003</v>
       </c>
       <c r="C3">
-        <v>71050.755999999994</v>
+        <v>71050.75599999999</v>
       </c>
       <c r="D3">
-        <v>158011.21200000009</v>
+        <v>158011.2120000001</v>
       </c>
       <c r="E3">
-        <v>154397.21299999999</v>
+        <v>154397.213</v>
       </c>
       <c r="F3">
-        <v>161797.57499999981</v>
+        <v>161797.5749999998</v>
       </c>
       <c r="G3">
-        <v>865035502.41800117</v>
+        <v>865035502.4180012</v>
       </c>
       <c r="H3">
-        <v>836710268.91499996</v>
+        <v>836710268.915</v>
+      </c>
+      <c r="I3">
+        <v>895045293.5889997</v>
       </c>
       <c r="J3">
-        <v>21014333824.206009</v>
+        <v>21014333824.20601</v>
       </c>
       <c r="K3">
-        <v>20542800374.775009</v>
+        <v>20542800374.77501</v>
       </c>
       <c r="L3">
         <v>21522856907.521</v>
       </c>
-      <c r="M3" t="s">
-        <v>14</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Modal shift scenario</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4">
-        <v>59192.679999999993</v>
+        <v>59192.67999999999</v>
       </c>
       <c r="B4">
-        <v>63567.055999999982</v>
+        <v>63567.05599999998</v>
       </c>
       <c r="C4">
-        <v>54581.286999999887</v>
+        <v>54581.28699999989</v>
       </c>
       <c r="D4">
-        <v>378940.92300000013</v>
+        <v>378940.9230000001</v>
       </c>
       <c r="E4">
-        <v>381107.54099999991</v>
+        <v>381107.5409999999</v>
       </c>
       <c r="F4">
-        <v>376174.31300000002</v>
+        <v>376174.313</v>
       </c>
       <c r="G4">
-        <v>880147950.77899981</v>
+        <v>880147950.7789998</v>
       </c>
       <c r="H4">
-        <v>935467385.11800003</v>
+        <v>935467385.118</v>
       </c>
       <c r="I4">
-        <v>821816747.11900043</v>
+        <v>821816747.1190004</v>
       </c>
       <c r="J4">
-        <v>50400560778.572998</v>
+        <v>50400560778.573</v>
       </c>
       <c r="K4">
-        <v>50685755987.375992</v>
+        <v>50685755987.37599</v>
       </c>
       <c r="L4">
-        <v>50033309856.325104</v>
-      </c>
-      <c r="M4" t="s">
-        <v>15</v>
+        <v>50033309856.3251</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Best practice scenario</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Scenarios/HIA_add_scenarios.xlsx
+++ b/output/Tables/Scenarios/HIA_add_scenarios.xlsx
@@ -1,21 +1,80 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Scenarios/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3C75C9-DF44-8E45-B5AC-D5D1C2422630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="24400" windowHeight="10960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>Best case scenario</t>
+  </si>
+  <si>
+    <t>Modal shift scenario</t>
+  </si>
+  <si>
+    <t>Best practice scenario</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +122,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +174,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +208,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +243,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,86 +419,75 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>749171.939</v>
+        <v>749171.93900000001</v>
       </c>
       <c r="B2">
-        <v>739181.1360000001</v>
+        <v>739181.13600000006</v>
       </c>
       <c r="C2">
-        <v>759107.7250000001</v>
+        <v>759107.72500000009</v>
       </c>
       <c r="D2">
         <v>1513284.632</v>
@@ -441,16 +499,16 @@
         <v>1529218.179</v>
       </c>
       <c r="G2">
-        <v>9585513523.317001</v>
+        <v>9585513523.3170013</v>
       </c>
       <c r="H2">
         <v>9431146725.460001</v>
       </c>
       <c r="I2">
-        <v>9741544352.556999</v>
+        <v>9741544352.5569992</v>
       </c>
       <c r="J2">
-        <v>201268309936.555</v>
+        <v>201268309936.55499</v>
       </c>
       <c r="K2">
         <v>199147675007.879</v>
@@ -458,96 +516,90 @@
       <c r="L2">
         <v>203379184933.759</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Best case scenario</t>
-        </is>
+      <c r="M2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>68790.304</v>
+        <v>68790.304000000004</v>
       </c>
       <c r="B3">
-        <v>66630.64900000003</v>
+        <v>66630.649000000034</v>
       </c>
       <c r="C3">
-        <v>71050.75599999999</v>
+        <v>71050.755999999994</v>
       </c>
       <c r="D3">
-        <v>158011.2120000001</v>
+        <v>158011.21200000009</v>
       </c>
       <c r="E3">
-        <v>154397.213</v>
+        <v>154397.21299999999</v>
       </c>
       <c r="F3">
-        <v>161797.5749999998</v>
+        <v>161797.57499999981</v>
       </c>
       <c r="G3">
-        <v>865035502.4180012</v>
+        <v>865035502.41800117</v>
       </c>
       <c r="H3">
-        <v>836710268.915</v>
+        <v>836710268.91499996</v>
       </c>
       <c r="I3">
-        <v>895045293.5889997</v>
+        <v>895045293.58899975</v>
       </c>
       <c r="J3">
-        <v>21014333824.20601</v>
+        <v>21014333824.206009</v>
       </c>
       <c r="K3">
-        <v>20542800374.77501</v>
+        <v>20542800374.775009</v>
       </c>
       <c r="L3">
         <v>21522856907.521</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Modal shift scenario</t>
-        </is>
+      <c r="M3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>59192.67999999999</v>
+        <v>59192.679999999993</v>
       </c>
       <c r="B4">
-        <v>63567.05599999998</v>
+        <v>63567.055999999982</v>
       </c>
       <c r="C4">
-        <v>54581.28699999989</v>
+        <v>54581.286999999887</v>
       </c>
       <c r="D4">
-        <v>378940.9230000001</v>
+        <v>378940.92300000013</v>
       </c>
       <c r="E4">
-        <v>381107.5409999999</v>
+        <v>381107.54099999991</v>
       </c>
       <c r="F4">
-        <v>376174.313</v>
+        <v>376174.31300000002</v>
       </c>
       <c r="G4">
-        <v>880147950.7789998</v>
+        <v>880147950.77899981</v>
       </c>
       <c r="H4">
-        <v>935467385.118</v>
+        <v>935467385.11800003</v>
       </c>
       <c r="I4">
-        <v>821816747.1190004</v>
+        <v>821816747.11900043</v>
       </c>
       <c r="J4">
-        <v>50400560778.573</v>
+        <v>50400560778.572998</v>
       </c>
       <c r="K4">
-        <v>50685755987.37599</v>
+        <v>50685755987.375992</v>
       </c>
       <c r="L4">
-        <v>50033309856.3251</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Best practice scenario</t>
-        </is>
+        <v>50033309856.325104</v>
+      </c>
+      <c r="M4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Scenarios/HIA_add_scenarios.xlsx
+++ b/output/Tables/Scenarios/HIA_add_scenarios.xlsx
@@ -1,80 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Scenarios/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3C75C9-DF44-8E45-B5AC-D5D1C2422630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="24400" windowHeight="10960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>scenario</t>
-  </si>
-  <si>
-    <t>Best case scenario</t>
-  </si>
-  <si>
-    <t>Modal shift scenario</t>
-  </si>
-  <si>
-    <t>Best practice scenario</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -174,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -208,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -243,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -419,75 +350,86 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2">
-        <v>749171.93900000001</v>
+        <v>749171.939</v>
       </c>
       <c r="B2">
-        <v>739181.13600000006</v>
+        <v>739181.1360000001</v>
       </c>
       <c r="C2">
-        <v>759107.72500000009</v>
+        <v>759107.7250000001</v>
       </c>
       <c r="D2">
         <v>1513284.632</v>
@@ -499,16 +441,16 @@
         <v>1529218.179</v>
       </c>
       <c r="G2">
-        <v>9585513523.3170013</v>
+        <v>9585513523.317001</v>
       </c>
       <c r="H2">
         <v>9431146725.460001</v>
       </c>
       <c r="I2">
-        <v>9741544352.5569992</v>
+        <v>9741544352.556999</v>
       </c>
       <c r="J2">
-        <v>201268309936.55499</v>
+        <v>201268309936.555</v>
       </c>
       <c r="K2">
         <v>199147675007.879</v>
@@ -516,90 +458,96 @@
       <c r="L2">
         <v>203379184933.759</v>
       </c>
-      <c r="M2" t="s">
-        <v>13</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Best case scenario</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3">
-        <v>68790.304000000004</v>
+        <v>68790.304</v>
       </c>
       <c r="B3">
-        <v>66630.649000000034</v>
+        <v>66630.64900000003</v>
       </c>
       <c r="C3">
-        <v>71050.755999999994</v>
+        <v>71050.75599999999</v>
       </c>
       <c r="D3">
-        <v>158011.21200000009</v>
+        <v>158011.2120000001</v>
       </c>
       <c r="E3">
-        <v>154397.21299999999</v>
+        <v>154397.213</v>
       </c>
       <c r="F3">
-        <v>161797.57499999981</v>
+        <v>161797.5749999998</v>
       </c>
       <c r="G3">
-        <v>865035502.41800117</v>
+        <v>865035502.4180012</v>
       </c>
       <c r="H3">
-        <v>836710268.91499996</v>
+        <v>836710268.915</v>
       </c>
       <c r="I3">
-        <v>895045293.58899975</v>
+        <v>895045293.5889997</v>
       </c>
       <c r="J3">
-        <v>21014333824.206009</v>
+        <v>21014333824.20601</v>
       </c>
       <c r="K3">
-        <v>20542800374.775009</v>
+        <v>20542800374.77501</v>
       </c>
       <c r="L3">
         <v>21522856907.521</v>
       </c>
-      <c r="M3" t="s">
-        <v>14</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Modal shift scenario</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4">
-        <v>59192.679999999993</v>
+        <v>193118.2689999999</v>
       </c>
       <c r="B4">
-        <v>63567.055999999982</v>
+        <v>188767.9449999999</v>
       </c>
       <c r="C4">
-        <v>54581.286999999887</v>
+        <v>197282.7129999999</v>
       </c>
       <c r="D4">
-        <v>378940.92300000013</v>
+        <v>596366.322</v>
       </c>
       <c r="E4">
-        <v>381107.54099999991</v>
+        <v>585981.6339999997</v>
       </c>
       <c r="F4">
-        <v>376174.31300000002</v>
+        <v>606408.748</v>
       </c>
       <c r="G4">
-        <v>880147950.77899981</v>
+        <v>2305725776.639</v>
       </c>
       <c r="H4">
-        <v>935467385.11800003</v>
+        <v>2266443421.789999</v>
       </c>
       <c r="I4">
-        <v>821816747.11900043</v>
+        <v>2343324287.537999</v>
       </c>
       <c r="J4">
-        <v>50400560778.572998</v>
+        <v>79318557723.62701</v>
       </c>
       <c r="K4">
-        <v>50685755987.375992</v>
+        <v>77942435556.5591</v>
       </c>
       <c r="L4">
-        <v>50033309856.325104</v>
-      </c>
-      <c r="M4" t="s">
-        <v>15</v>
+        <v>80660270590.14401</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Best practice scenario</t>
+        </is>
       </c>
     </row>
   </sheetData>
